--- a/AAII_Financials/Yearly/OPTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OPTU_YR_FIN.xlsx
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1710600</v>
+        <v>1675600</v>
       </c>
       <c r="E14" s="3">
-        <v>35900</v>
+        <v>25100</v>
       </c>
       <c r="F14" s="3">
-        <v>196600</v>
+        <v>191400</v>
       </c>
       <c r="G14" s="3">
         <v>364800</v>
@@ -946,13 +946,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7015900</v>
+        <v>7050900</v>
       </c>
       <c r="E17" s="3">
-        <v>7250600</v>
+        <v>7261400</v>
       </c>
       <c r="F17" s="3">
-        <v>7320400</v>
+        <v>7325600</v>
       </c>
       <c r="G17" s="3">
         <v>7714800</v>
@@ -976,13 +976,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1574600</v>
+        <v>1539500</v>
       </c>
       <c r="E18" s="3">
-        <v>1703800</v>
+        <v>1693000</v>
       </c>
       <c r="F18" s="3">
-        <v>1916700</v>
+        <v>1911500</v>
       </c>
       <c r="G18" s="3">
         <v>1932900</v>
@@ -1050,13 +1050,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3268500</v>
+        <v>3233400</v>
       </c>
       <c r="E21" s="3">
-        <v>3340300</v>
+        <v>3329600</v>
       </c>
       <c r="F21" s="3">
-        <v>3565900</v>
+        <v>3560700</v>
       </c>
       <c r="G21" s="3">
         <v>3715100</v>
